--- a/docs/deliverables/03_内部設計/内部設計書.xlsx
+++ b/docs/deliverables/03_内部設計/内部設計書.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Rfb54185b32f54910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム構成" sheetId="2" r:id="R12bc4241ad60435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バックエンド構造" sheetId="3" r:id="Re919c7f5e41f4bf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データモデル" sheetId="4" r:id="R801965c9f8164640"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務時間計算" sheetId="5" r:id="R9d59b0e2f75e4593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証・認可設計" sheetId="6" r:id="Rae75d20c5fd8414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web・ファイルセキュリティ" sheetId="7" r:id="R5651a72f07e0459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コンテナ・ネットワーク設計" sheetId="8" r:id="R95402d7640c840d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ログ・監査" sheetId="9" r:id="Rf6a014af8c32441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同時更新" sheetId="10" r:id="R7cc39e643e6c4510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB移行" sheetId="11" r:id="Rec88d8ed92cb4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文書管理" sheetId="1" r:id="Rc5844ec8e7bd444e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="システム構成" sheetId="2" r:id="R7d43877786e44675"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="バックエンド構造" sheetId="3" r:id="R8d9d51b76ab34eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="データモデル" sheetId="4" r:id="Rfc5c618c26344c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務時間計算" sheetId="5" r:id="Rf6f4b874124f4731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証・認可設計" sheetId="6" r:id="R5cf0df67c440475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web・ファイルセキュリティ" sheetId="7" r:id="Rcf79e8fba2774c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コンテナ・ネットワーク設計" sheetId="8" r:id="Rb7c2d15622d440f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ログ・監査" sheetId="9" r:id="R196965299e5c4257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="同時更新" sheetId="10" r:id="R47d93c21816e4725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB移行" sheetId="11" r:id="Rd9406d62ce0346e7"/>
   </x:sheets>
 </x:workbook>
 </file>
